--- a/static/data/exports/Retro_MN_GE_2014.xlsx
+++ b/static/data/exports/Retro_MN_GE_2014.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -883,7 +883,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -3668,7 +3668,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P74" t="n">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P85" t="n">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P87" t="n">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P97" t="n">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P103" t="n">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P119" t="n">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P134" t="n">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P135" t="n">
@@ -10438,7 +10438,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P137" t="n">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P145" t="n">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P146" t="n">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -11325,7 +11325,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P148" t="n">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P152" t="n">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P154" t="n">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P155" t="n">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P156" t="n">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P157" t="n">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P158" t="n">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P160" t="n">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P161" t="n">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -12424,7 +12424,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P163" t="n">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P165" t="n">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P166" t="n">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P168" t="n">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P169" t="n">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P170" t="n">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P171" t="n">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P172" t="n">
@@ -13161,7 +13161,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P173" t="n">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P174" t="n">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P175" t="n">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P176" t="n">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P177" t="n">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -13673,7 +13673,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P180" t="n">
@@ -13748,7 +13748,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P181" t="n">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -13898,7 +13898,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P183" t="n">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -14048,7 +14048,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -14123,7 +14123,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P186" t="n">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P187" t="n">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P189" t="n">
@@ -14410,7 +14410,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P190" t="n">
@@ -14485,7 +14485,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P191" t="n">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P192" t="n">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P193" t="n">
@@ -14710,7 +14710,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P194" t="n">
@@ -14785,7 +14785,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P195" t="n">
@@ -14922,7 +14922,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P197" t="n">
@@ -14997,7 +14997,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P199" t="n">
@@ -15147,7 +15147,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P200" t="n">
@@ -15222,7 +15222,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P201" t="n">
@@ -15297,7 +15297,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P202" t="n">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P203" t="n">
@@ -15447,7 +15447,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P204" t="n">
@@ -15522,7 +15522,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P205" t="n">
@@ -15659,7 +15659,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P207" t="n">
@@ -15734,7 +15734,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P208" t="n">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P209" t="n">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P210" t="n">
@@ -15959,7 +15959,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P211" t="n">
@@ -16034,7 +16034,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P212" t="n">
@@ -16171,7 +16171,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P214" t="n">
@@ -16246,7 +16246,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P215" t="n">
@@ -16321,7 +16321,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P216" t="n">
@@ -16396,7 +16396,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P217" t="n">
@@ -16471,7 +16471,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P218" t="n">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P219" t="n">
@@ -16621,7 +16621,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P220" t="n">
@@ -16696,7 +16696,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P221" t="n">
@@ -16771,7 +16771,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P222" t="n">
@@ -16908,7 +16908,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P224" t="n">
@@ -16983,7 +16983,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P225" t="n">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P226" t="n">
@@ -17133,7 +17133,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P227" t="n">
@@ -17208,7 +17208,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P228" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P229" t="n">
@@ -17358,7 +17358,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P230" t="n">
@@ -17495,7 +17495,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P232" t="n">
@@ -17570,7 +17570,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P233" t="n">
@@ -17645,7 +17645,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P234" t="n">
@@ -17720,7 +17720,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P235" t="n">
@@ -17795,7 +17795,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P236" t="n">
@@ -17870,7 +17870,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P237" t="n">
@@ -17945,7 +17945,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P238" t="n">
@@ -18020,7 +18020,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P239" t="n">
@@ -18095,7 +18095,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P240" t="n">
@@ -18170,7 +18170,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -18307,7 +18307,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P243" t="n">
@@ -18382,7 +18382,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P244" t="n">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P245" t="n">
@@ -18532,7 +18532,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P246" t="n">
@@ -18607,7 +18607,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P247" t="n">
@@ -18682,7 +18682,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P248" t="n">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P249" t="n">
@@ -18832,7 +18832,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P250" t="n">
@@ -18969,7 +18969,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P252" t="n">
@@ -19044,7 +19044,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P253" t="n">
@@ -19119,7 +19119,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P254" t="n">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P255" t="n">
@@ -19269,7 +19269,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P256" t="n">
@@ -19344,7 +19344,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P257" t="n">
@@ -19419,7 +19419,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P258" t="n">
@@ -19556,7 +19556,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P260" t="n">
@@ -19631,7 +19631,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P261" t="n">
@@ -19706,7 +19706,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P262" t="n">
@@ -19781,7 +19781,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P263" t="n">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P264" t="n">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P265" t="n">
@@ -20006,7 +20006,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P266" t="n">
@@ -20081,7 +20081,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P267" t="n">
@@ -20218,7 +20218,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P269" t="n">
@@ -20293,7 +20293,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P270" t="n">
@@ -20368,7 +20368,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P271" t="n">
@@ -20443,7 +20443,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P272" t="n">
@@ -20518,7 +20518,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P273" t="n">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P274" t="n">
@@ -20668,7 +20668,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P275" t="n">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P277" t="n">
@@ -20880,7 +20880,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P278" t="n">
@@ -20955,7 +20955,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P279" t="n">
@@ -21030,7 +21030,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P280" t="n">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P281" t="n">
@@ -21180,7 +21180,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P282" t="n">
@@ -21255,7 +21255,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P283" t="n">
@@ -21330,7 +21330,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P284" t="n">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P285" t="n">
@@ -21480,7 +21480,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P286" t="n">
@@ -21617,7 +21617,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P288" t="n">
@@ -21692,7 +21692,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P289" t="n">
@@ -21767,7 +21767,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P290" t="n">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P291" t="n">
@@ -21917,7 +21917,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P292" t="n">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P293" t="n">
@@ -22067,7 +22067,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P294" t="n">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P296" t="n">
@@ -22227,20 +22227,20 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>1711074</v>
+        <v>1711073</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Lamminlien Lien Gangte</t>
+          <t>Lamlalmoi Momoi Gangte</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>JD(U)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>19793</v>
+        <v>19781</v>
       </c>
       <c r="E297" t="n">
         <v>38</v>
@@ -22264,12 +22264,12 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Lamminlien Lien Gangte</t>
+          <t>Lamlalmoi Momoi Gangte</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>JD(U)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -22279,11 +22279,11 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P297" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="Q297" t="b">
         <v>0</v>
@@ -22302,20 +22302,20 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>1711073</v>
+        <v>1711074</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Lamlalmoi Momoi Gangte</t>
+          <t>Lamminlien Lien Gangte</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>JD(U)</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>19781</v>
+        <v>19793</v>
       </c>
       <c r="E298" t="n">
         <v>38</v>
@@ -22339,12 +22339,12 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>Lamlalmoi Momoi Gangte</t>
+          <t>Lamminlien Lien Gangte</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>JD(U)</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -22354,11 +22354,11 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P298" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="Q298" t="b">
         <v>0</v>
@@ -22429,7 +22429,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P299" t="n">
@@ -22504,7 +22504,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P300" t="n">
@@ -22579,7 +22579,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P301" t="n">
@@ -22654,7 +22654,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P302" t="n">
@@ -22729,7 +22729,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P303" t="n">
@@ -22804,7 +22804,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P304" t="n">
@@ -22879,7 +22879,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P305" t="n">
@@ -23016,7 +23016,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P307" t="n">
@@ -23091,7 +23091,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P308" t="n">
@@ -23166,7 +23166,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P309" t="n">
@@ -23189,20 +23189,20 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>1711087</v>
+        <v>1711086</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Lamminlien Lien Gangte</t>
+          <t>Amarson Sankhil</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>JD(U)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>19793</v>
+        <v>19781</v>
       </c>
       <c r="E310" t="n">
         <v>12</v>
@@ -23226,12 +23226,12 @@
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>Lamminlien Lien Gangte</t>
+          <t>Amarson Sankhil</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>JD(U)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -23241,11 +23241,11 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P310" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q310" t="b">
         <v>0</v>
@@ -23264,20 +23264,20 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>1711086</v>
+        <v>1711087</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Amarson Sankhil</t>
+          <t>Lamminlien Lien Gangte</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>JD(U)</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>19781</v>
+        <v>19793</v>
       </c>
       <c r="E311" t="n">
         <v>12</v>
@@ -23301,12 +23301,12 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>Amarson Sankhil</t>
+          <t>Lamminlien Lien Gangte</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>JD(U)</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -23316,11 +23316,11 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P311" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Q311" t="b">
         <v>0</v>
@@ -23391,7 +23391,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P312" t="n">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P313" t="n">
@@ -23541,7 +23541,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P314" t="n">
@@ -23616,7 +23616,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P315" t="n">
@@ -23753,7 +23753,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P318" t="n">
@@ -23903,7 +23903,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P319" t="n">
@@ -23978,7 +23978,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P320" t="n">
@@ -24053,7 +24053,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P321" t="n">
@@ -24128,7 +24128,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P322" t="n">
@@ -24203,7 +24203,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P323" t="n">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P324" t="n">
@@ -24353,7 +24353,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P325" t="n">
@@ -24428,7 +24428,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P326" t="n">
@@ -24503,7 +24503,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P327" t="n">
@@ -24578,7 +24578,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P328" t="n">
@@ -24715,7 +24715,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P330" t="n">
@@ -24790,7 +24790,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P331" t="n">
@@ -24865,7 +24865,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P332" t="n">
@@ -24940,7 +24940,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P333" t="n">
@@ -25015,7 +25015,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P334" t="n">
@@ -25090,7 +25090,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P335" t="n">
@@ -25165,7 +25165,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P336" t="n">
@@ -25240,7 +25240,7 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P337" t="n">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P338" t="n">
@@ -25452,7 +25452,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P340" t="n">
@@ -25527,7 +25527,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P341" t="n">
@@ -25602,7 +25602,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P342" t="n">
@@ -25677,7 +25677,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P343" t="n">
@@ -25752,7 +25752,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P344" t="n">
@@ -25827,7 +25827,7 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P345" t="n">
@@ -25902,7 +25902,7 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P346" t="n">
@@ -25977,7 +25977,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P347" t="n">
@@ -26052,7 +26052,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P348" t="n">
@@ -26127,7 +26127,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P349" t="n">
@@ -26202,7 +26202,7 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P350" t="n">
@@ -26339,7 +26339,7 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P352" t="n">
@@ -26414,7 +26414,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P353" t="n">
@@ -26489,7 +26489,7 @@
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P354" t="n">
@@ -26564,7 +26564,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P355" t="n">
@@ -26639,7 +26639,7 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P356" t="n">
@@ -26714,7 +26714,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P357" t="n">
@@ -26789,7 +26789,7 @@
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P358" t="n">
@@ -26864,7 +26864,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P359" t="n">
@@ -26939,7 +26939,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P360" t="n">
@@ -27014,7 +27014,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P361" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P363" t="n">
@@ -27226,7 +27226,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P364" t="n">
@@ -27249,20 +27249,20 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>1711142</v>
+        <v>1711141</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Lamminlien Lien Gangte</t>
+          <t>Lamlalmoi Momoi Gangte</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>JD(U)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>19793</v>
+        <v>19781</v>
       </c>
       <c r="E365" t="n">
         <v>13</v>
@@ -27286,12 +27286,12 @@
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>Lamminlien Lien Gangte</t>
+          <t>Lamlalmoi Momoi Gangte</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>JD(U)</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -27301,11 +27301,11 @@
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P365" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="Q365" t="b">
         <v>0</v>
@@ -27324,20 +27324,20 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>1711141</v>
+        <v>1711142</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Lamlalmoi Momoi Gangte</t>
+          <t>Lamminlien Lien Gangte</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>JD(U)</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>19781</v>
+        <v>19793</v>
       </c>
       <c r="E366" t="n">
         <v>13</v>
@@ -27361,12 +27361,12 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>Lamlalmoi Momoi Gangte</t>
+          <t>Lamminlien Lien Gangte</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>JD(U)</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -27376,11 +27376,11 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P366" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="Q366" t="b">
         <v>0</v>
@@ -27451,7 +27451,7 @@
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P367" t="n">
@@ -27526,7 +27526,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P368" t="n">
@@ -27601,7 +27601,7 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P369" t="n">
@@ -27676,7 +27676,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P370" t="n">
@@ -27751,7 +27751,7 @@
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P371" t="n">
@@ -27888,7 +27888,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P373" t="n">
@@ -27963,7 +27963,7 @@
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P374" t="n">
@@ -28038,7 +28038,7 @@
       </c>
       <c r="O375" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P375" t="n">
@@ -28113,7 +28113,7 @@
       </c>
       <c r="O376" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P376" t="n">
@@ -28188,7 +28188,7 @@
       </c>
       <c r="O377" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P377" t="n">
@@ -28263,7 +28263,7 @@
       </c>
       <c r="O378" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P378" t="n">
@@ -28338,7 +28338,7 @@
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P379" t="n">
@@ -28413,7 +28413,7 @@
       </c>
       <c r="O380" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P380" t="n">
@@ -28488,7 +28488,7 @@
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P381" t="n">
@@ -28563,7 +28563,7 @@
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P382" t="n">
@@ -28638,7 +28638,7 @@
       </c>
       <c r="O383" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P383" t="n">
@@ -28713,7 +28713,7 @@
       </c>
       <c r="O384" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P384" t="n">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P385" t="n">
@@ -28925,7 +28925,7 @@
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P387" t="n">
@@ -29000,7 +29000,7 @@
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P388" t="n">
@@ -29075,7 +29075,7 @@
       </c>
       <c r="O389" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P389" t="n">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="O390" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P390" t="n">
@@ -29225,7 +29225,7 @@
       </c>
       <c r="O391" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P391" t="n">
@@ -29300,7 +29300,7 @@
       </c>
       <c r="O392" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P392" t="n">
@@ -29375,7 +29375,7 @@
       </c>
       <c r="O393" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P393" t="n">
@@ -29450,7 +29450,7 @@
       </c>
       <c r="O394" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P394" t="n">
@@ -29525,7 +29525,7 @@
       </c>
       <c r="O395" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P395" t="n">
@@ -29600,7 +29600,7 @@
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P396" t="n">
@@ -29737,7 +29737,7 @@
       </c>
       <c r="O398" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P398" t="n">
@@ -29812,7 +29812,7 @@
       </c>
       <c r="O399" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P399" t="n">
@@ -29887,7 +29887,7 @@
       </c>
       <c r="O400" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P400" t="n">
@@ -29962,7 +29962,7 @@
       </c>
       <c r="O401" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P401" t="n">
@@ -30037,7 +30037,7 @@
       </c>
       <c r="O402" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P402" t="n">
@@ -30112,7 +30112,7 @@
       </c>
       <c r="O403" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P403" t="n">
@@ -30187,7 +30187,7 @@
       </c>
       <c r="O404" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P404" t="n">
@@ -30262,7 +30262,7 @@
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P405" t="n">
@@ -30337,7 +30337,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P406" t="n">
@@ -30412,7 +30412,7 @@
       </c>
       <c r="O407" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P407" t="n">
@@ -30549,7 +30549,7 @@
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P409" t="n">
@@ -30624,7 +30624,7 @@
       </c>
       <c r="O410" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P410" t="n">
@@ -30699,7 +30699,7 @@
       </c>
       <c r="O411" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P411" t="n">
@@ -30774,7 +30774,7 @@
       </c>
       <c r="O412" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P412" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="O413" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P413" t="n">
@@ -30924,7 +30924,7 @@
       </c>
       <c r="O414" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P414" t="n">
@@ -30999,7 +30999,7 @@
       </c>
       <c r="O415" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P415" t="n">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="O416" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P416" t="n">
@@ -31149,7 +31149,7 @@
       </c>
       <c r="O417" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P417" t="n">
@@ -31286,7 +31286,7 @@
       </c>
       <c r="O419" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P419" t="n">
@@ -31361,7 +31361,7 @@
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P420" t="n">
@@ -31436,7 +31436,7 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P421" t="n">
@@ -31511,7 +31511,7 @@
       </c>
       <c r="O422" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P422" t="n">
@@ -31586,7 +31586,7 @@
       </c>
       <c r="O423" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P423" t="n">
@@ -31661,7 +31661,7 @@
       </c>
       <c r="O424" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P424" t="n">
@@ -31736,7 +31736,7 @@
       </c>
       <c r="O425" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P425" t="n">
@@ -31873,7 +31873,7 @@
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P427" t="n">
@@ -31948,7 +31948,7 @@
       </c>
       <c r="O428" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P428" t="n">
@@ -32023,7 +32023,7 @@
       </c>
       <c r="O429" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P429" t="n">
@@ -32098,7 +32098,7 @@
       </c>
       <c r="O430" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P430" t="n">
@@ -32173,7 +32173,7 @@
       </c>
       <c r="O431" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P431" t="n">
@@ -32248,7 +32248,7 @@
       </c>
       <c r="O432" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P432" t="n">
@@ -32323,7 +32323,7 @@
       </c>
       <c r="O433" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P433" t="n">
@@ -32398,7 +32398,7 @@
       </c>
       <c r="O434" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P434" t="n">
@@ -32473,7 +32473,7 @@
       </c>
       <c r="O435" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P435" t="n">
@@ -32548,7 +32548,7 @@
       </c>
       <c r="O436" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P436" t="n">
@@ -32623,7 +32623,7 @@
       </c>
       <c r="O437" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P437" t="n">
@@ -32698,7 +32698,7 @@
       </c>
       <c r="O438" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P438" t="n">
@@ -32773,7 +32773,7 @@
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P439" t="n">
@@ -32910,7 +32910,7 @@
       </c>
       <c r="O441" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P441" t="n">
@@ -32985,7 +32985,7 @@
       </c>
       <c r="O442" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P442" t="n">
@@ -33060,7 +33060,7 @@
       </c>
       <c r="O443" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P443" t="n">
@@ -33135,7 +33135,7 @@
       </c>
       <c r="O444" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P444" t="n">
@@ -33210,7 +33210,7 @@
       </c>
       <c r="O445" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P445" t="n">
@@ -33285,7 +33285,7 @@
       </c>
       <c r="O446" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P446" t="n">
@@ -33360,7 +33360,7 @@
       </c>
       <c r="O447" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P447" t="n">
@@ -33435,7 +33435,7 @@
       </c>
       <c r="O448" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P448" t="n">
@@ -33510,7 +33510,7 @@
       </c>
       <c r="O449" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P449" t="n">
@@ -33585,7 +33585,7 @@
       </c>
       <c r="O450" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P450" t="n">
@@ -33608,20 +33608,20 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>1711228</v>
+        <v>1711227</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Lamlalmoi Momoi Gangte</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>NOTA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>19789</v>
+        <v>19781</v>
       </c>
       <c r="E451" t="n">
         <v>6</v>
@@ -33645,13 +33645,26 @@
       </c>
       <c r="K451" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Lamlalmoi Momoi Gangte</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>NOTA</t>
-        </is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P451" t="n">
+        <v>38</v>
       </c>
       <c r="Q451" t="b">
         <v>0</v>
@@ -33670,20 +33683,20 @@
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>1711227</v>
+        <v>1711228</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Lamlalmoi Momoi Gangte</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NOTA</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>19781</v>
+        <v>19789</v>
       </c>
       <c r="E452" t="n">
         <v>6</v>
@@ -33707,26 +33720,13 @@
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>Lamlalmoi Momoi Gangte</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
         <is>
-          <t>IND</t>
-        </is>
-      </c>
-      <c r="N452" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="O452" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="P452" t="n">
-        <v>38</v>
+          <t>NOTA</t>
+        </is>
       </c>
       <c r="Q452" t="b">
         <v>0</v>
@@ -33797,7 +33797,7 @@
       </c>
       <c r="O453" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P453" t="n">
@@ -33872,7 +33872,7 @@
       </c>
       <c r="O454" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P454" t="n">
@@ -33947,7 +33947,7 @@
       </c>
       <c r="O455" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P455" t="n">
@@ -34022,7 +34022,7 @@
       </c>
       <c r="O456" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P456" t="n">
@@ -34097,7 +34097,7 @@
       </c>
       <c r="O457" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P457" t="n">
@@ -34172,7 +34172,7 @@
       </c>
       <c r="O458" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P458" t="n">
@@ -34195,20 +34195,20 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>1711235</v>
+        <v>1711236</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Kim Gangte</t>
+          <t>M. Khamchinpau K. Zou</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>AITC</t>
+          <t>AAAP</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>19787</v>
+        <v>19790</v>
       </c>
       <c r="E459" t="n">
         <v>24</v>
@@ -34232,12 +34232,12 @@
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t>Kim Gangte</t>
+          <t>M. Khamchinpau K. Zou</t>
         </is>
       </c>
       <c r="L459" t="inlineStr">
         <is>
-          <t>AITC</t>
+          <t>AAAP</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -34247,11 +34247,11 @@
       </c>
       <c r="O459" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P459" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q459" t="b">
         <v>0</v>
@@ -34270,20 +34270,20 @@
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>1711236</v>
+        <v>1711235</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>M. Khamchinpau K. Zou</t>
+          <t>Kim Gangte</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>AAAP</t>
+          <t>AITC</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>19790</v>
+        <v>19787</v>
       </c>
       <c r="E460" t="n">
         <v>24</v>
@@ -34307,12 +34307,12 @@
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>M. Khamchinpau K. Zou</t>
+          <t>Kim Gangte</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>AAAP</t>
+          <t>AITC</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -34322,11 +34322,11 @@
       </c>
       <c r="O460" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P460" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q460" t="b">
         <v>0</v>
@@ -34397,7 +34397,7 @@
       </c>
       <c r="O461" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P461" t="n">
@@ -34472,7 +34472,7 @@
       </c>
       <c r="O462" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P462" t="n">
@@ -34609,7 +34609,7 @@
       </c>
       <c r="O464" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P464" t="n">
@@ -34684,7 +34684,7 @@
       </c>
       <c r="O465" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P465" t="n">
@@ -34759,7 +34759,7 @@
       </c>
       <c r="O466" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P466" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="O467" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P467" t="n">
@@ -34909,7 +34909,7 @@
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P468" t="n">
@@ -34984,7 +34984,7 @@
       </c>
       <c r="O469" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P469" t="n">
@@ -35059,7 +35059,7 @@
       </c>
       <c r="O470" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P470" t="n">
@@ -35134,7 +35134,7 @@
       </c>
       <c r="O471" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P471" t="n">
@@ -35271,7 +35271,7 @@
       </c>
       <c r="O473" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P473" t="n">
@@ -35346,7 +35346,7 @@
       </c>
       <c r="O474" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P474" t="n">
@@ -35421,7 +35421,7 @@
       </c>
       <c r="O475" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P475" t="n">
@@ -35496,7 +35496,7 @@
       </c>
       <c r="O476" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P476" t="n">
@@ -35571,7 +35571,7 @@
       </c>
       <c r="O477" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P477" t="n">
@@ -35646,7 +35646,7 @@
       </c>
       <c r="O478" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P478" t="n">
@@ -35721,7 +35721,7 @@
       </c>
       <c r="O479" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P479" t="n">
@@ -35796,7 +35796,7 @@
       </c>
       <c r="O480" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P480" t="n">
@@ -35871,7 +35871,7 @@
       </c>
       <c r="O481" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P481" t="n">
@@ -35946,7 +35946,7 @@
       </c>
       <c r="O482" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P482" t="n">
@@ -36021,7 +36021,7 @@
       </c>
       <c r="O483" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P483" t="n">
@@ -36158,7 +36158,7 @@
       </c>
       <c r="O485" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P485" t="n">
@@ -36233,7 +36233,7 @@
       </c>
       <c r="O486" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P486" t="n">
@@ -36308,7 +36308,7 @@
       </c>
       <c r="O487" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P487" t="n">
@@ -36383,7 +36383,7 @@
       </c>
       <c r="O488" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P488" t="n">
@@ -36458,7 +36458,7 @@
       </c>
       <c r="O489" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P489" t="n">
@@ -36533,7 +36533,7 @@
       </c>
       <c r="O490" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P490" t="n">
@@ -36608,7 +36608,7 @@
       </c>
       <c r="O491" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P491" t="n">
@@ -36683,7 +36683,7 @@
       </c>
       <c r="O492" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P492" t="n">
@@ -36758,7 +36758,7 @@
       </c>
       <c r="O493" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P493" t="n">
@@ -36833,7 +36833,7 @@
       </c>
       <c r="O494" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P494" t="n">
@@ -36970,7 +36970,7 @@
       </c>
       <c r="O496" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P496" t="n">
@@ -37045,7 +37045,7 @@
       </c>
       <c r="O497" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P497" t="n">
@@ -37120,7 +37120,7 @@
       </c>
       <c r="O498" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P498" t="n">
@@ -37195,7 +37195,7 @@
       </c>
       <c r="O499" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P499" t="n">
@@ -37270,7 +37270,7 @@
       </c>
       <c r="O500" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P500" t="n">
@@ -37345,7 +37345,7 @@
       </c>
       <c r="O501" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P501" t="n">
@@ -37420,7 +37420,7 @@
       </c>
       <c r="O502" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P502" t="n">
@@ -37495,7 +37495,7 @@
       </c>
       <c r="O503" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P503" t="n">
@@ -37570,7 +37570,7 @@
       </c>
       <c r="O504" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P504" t="n">
@@ -37645,7 +37645,7 @@
       </c>
       <c r="O505" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P505" t="n">
@@ -37668,20 +37668,20 @@
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>1711283</v>
+        <v>1711282</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>M. Khamchinpau K. Zou</t>
+          <t>Lamminlien Lien Gangte</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>AAAP</t>
+          <t>JD(U)</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>19790</v>
+        <v>19793</v>
       </c>
       <c r="E506" t="n">
         <v>19</v>
@@ -37705,12 +37705,12 @@
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t>M. Khamchinpau K. Zou</t>
+          <t>Lamminlien Lien Gangte</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>AAAP</t>
+          <t>JD(U)</t>
         </is>
       </c>
       <c r="N506" t="inlineStr">
@@ -37720,11 +37720,11 @@
       </c>
       <c r="O506" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P506" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="Q506" t="b">
         <v>0</v>
@@ -37743,20 +37743,20 @@
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>1711282</v>
+        <v>1711283</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Lamminlien Lien Gangte</t>
+          <t>M. Khamchinpau K. Zou</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>JD(U)</t>
+          <t>AAAP</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>19793</v>
+        <v>19790</v>
       </c>
       <c r="E507" t="n">
         <v>19</v>
@@ -37780,12 +37780,12 @@
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>Lamminlien Lien Gangte</t>
+          <t>M. Khamchinpau K. Zou</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>JD(U)</t>
+          <t>AAAP</t>
         </is>
       </c>
       <c r="N507" t="inlineStr">
@@ -37795,11 +37795,11 @@
       </c>
       <c r="O507" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P507" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Q507" t="b">
         <v>0</v>
@@ -37932,7 +37932,7 @@
       </c>
       <c r="O509" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P509" t="n">
@@ -38007,7 +38007,7 @@
       </c>
       <c r="O510" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P510" t="n">
@@ -38082,7 +38082,7 @@
       </c>
       <c r="O511" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P511" t="n">
@@ -38157,7 +38157,7 @@
       </c>
       <c r="O512" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P512" t="n">
@@ -38232,7 +38232,7 @@
       </c>
       <c r="O513" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P513" t="n">
@@ -38307,7 +38307,7 @@
       </c>
       <c r="O514" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P514" t="n">
@@ -38382,7 +38382,7 @@
       </c>
       <c r="O515" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P515" t="n">
@@ -38519,7 +38519,7 @@
       </c>
       <c r="O517" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P517" t="n">
@@ -38594,7 +38594,7 @@
       </c>
       <c r="O518" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P518" t="n">
@@ -38669,7 +38669,7 @@
       </c>
       <c r="O519" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P519" t="n">
@@ -38744,7 +38744,7 @@
       </c>
       <c r="O520" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P520" t="n">
@@ -38819,7 +38819,7 @@
       </c>
       <c r="O521" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P521" t="n">
@@ -38894,7 +38894,7 @@
       </c>
       <c r="O522" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P522" t="n">
@@ -38969,7 +38969,7 @@
       </c>
       <c r="O523" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P523" t="n">
@@ -39044,7 +39044,7 @@
       </c>
       <c r="O524" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P524" t="n">
@@ -39119,7 +39119,7 @@
       </c>
       <c r="O525" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P525" t="n">
@@ -39194,7 +39194,7 @@
       </c>
       <c r="O526" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P526" t="n">
@@ -39269,7 +39269,7 @@
       </c>
       <c r="O527" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P527" t="n">
@@ -39344,7 +39344,7 @@
       </c>
       <c r="O528" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P528" t="n">
@@ -39481,7 +39481,7 @@
       </c>
       <c r="O530" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P530" t="n">
@@ -39556,7 +39556,7 @@
       </c>
       <c r="O531" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P531" t="n">
@@ -39631,7 +39631,7 @@
       </c>
       <c r="O532" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P532" t="n">
@@ -39706,7 +39706,7 @@
       </c>
       <c r="O533" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P533" t="n">
@@ -39781,7 +39781,7 @@
       </c>
       <c r="O534" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P534" t="n">
@@ -39856,7 +39856,7 @@
       </c>
       <c r="O535" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P535" t="n">
@@ -39931,7 +39931,7 @@
       </c>
       <c r="O536" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P536" t="n">
@@ -40006,7 +40006,7 @@
       </c>
       <c r="O537" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P537" t="n">
@@ -40081,7 +40081,7 @@
       </c>
       <c r="O538" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P538" t="n">
@@ -40156,7 +40156,7 @@
       </c>
       <c r="O539" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P539" t="n">
@@ -40231,7 +40231,7 @@
       </c>
       <c r="O540" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P540" t="n">
@@ -40306,7 +40306,7 @@
       </c>
       <c r="O541" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P541" t="n">
@@ -40443,7 +40443,7 @@
       </c>
       <c r="O543" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P543" t="n">
@@ -40518,7 +40518,7 @@
       </c>
       <c r="O544" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P544" t="n">
@@ -40593,7 +40593,7 @@
       </c>
       <c r="O545" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P545" t="n">
@@ -40668,7 +40668,7 @@
       </c>
       <c r="O546" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P546" t="n">
@@ -40743,7 +40743,7 @@
       </c>
       <c r="O547" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P547" t="n">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="O548" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P548" t="n">
@@ -40893,7 +40893,7 @@
       </c>
       <c r="O549" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P549" t="n">
@@ -40968,7 +40968,7 @@
       </c>
       <c r="O550" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P550" t="n">
@@ -41043,7 +41043,7 @@
       </c>
       <c r="O551" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P551" t="n">
@@ -41180,7 +41180,7 @@
       </c>
       <c r="O553" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P553" t="n">
@@ -41255,7 +41255,7 @@
       </c>
       <c r="O554" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P554" t="n">
@@ -41330,7 +41330,7 @@
       </c>
       <c r="O555" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P555" t="n">
@@ -41405,7 +41405,7 @@
       </c>
       <c r="O556" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P556" t="n">
@@ -41480,7 +41480,7 @@
       </c>
       <c r="O557" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P557" t="n">
@@ -41555,7 +41555,7 @@
       </c>
       <c r="O558" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P558" t="n">
@@ -41630,7 +41630,7 @@
       </c>
       <c r="O559" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P559" t="n">
@@ -41705,7 +41705,7 @@
       </c>
       <c r="O560" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P560" t="n">
@@ -41780,7 +41780,7 @@
       </c>
       <c r="O561" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P561" t="n">
@@ -41917,7 +41917,7 @@
       </c>
       <c r="O563" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P563" t="n">
@@ -41992,7 +41992,7 @@
       </c>
       <c r="O564" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P564" t="n">
@@ -42067,7 +42067,7 @@
       </c>
       <c r="O565" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P565" t="n">
@@ -42142,7 +42142,7 @@
       </c>
       <c r="O566" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P566" t="n">
@@ -42217,7 +42217,7 @@
       </c>
       <c r="O567" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P567" t="n">
@@ -42292,7 +42292,7 @@
       </c>
       <c r="O568" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P568" t="n">
@@ -42367,7 +42367,7 @@
       </c>
       <c r="O569" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P569" t="n">
@@ -42442,7 +42442,7 @@
       </c>
       <c r="O570" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P570" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="O571" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P571" t="n">
@@ -42654,7 +42654,7 @@
       </c>
       <c r="O573" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P573" t="n">
@@ -42729,7 +42729,7 @@
       </c>
       <c r="O574" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P574" t="n">
@@ -42804,7 +42804,7 @@
       </c>
       <c r="O575" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P575" t="n">
@@ -42879,7 +42879,7 @@
       </c>
       <c r="O576" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P576" t="n">
@@ -42954,7 +42954,7 @@
       </c>
       <c r="O577" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P577" t="n">
@@ -43029,7 +43029,7 @@
       </c>
       <c r="O578" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P578" t="n">
@@ -43104,7 +43104,7 @@
       </c>
       <c r="O579" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P579" t="n">
@@ -43179,7 +43179,7 @@
       </c>
       <c r="O580" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P580" t="n">
@@ -43254,7 +43254,7 @@
       </c>
       <c r="O581" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P581" t="n">
@@ -43329,7 +43329,7 @@
       </c>
       <c r="O582" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P582" t="n">
@@ -43404,7 +43404,7 @@
       </c>
       <c r="O583" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P583" t="n">
@@ -43541,7 +43541,7 @@
       </c>
       <c r="O585" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P585" t="n">
@@ -43616,7 +43616,7 @@
       </c>
       <c r="O586" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P586" t="n">
@@ -43691,7 +43691,7 @@
       </c>
       <c r="O587" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P587" t="n">
@@ -43766,7 +43766,7 @@
       </c>
       <c r="O588" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P588" t="n">
@@ -43841,7 +43841,7 @@
       </c>
       <c r="O589" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P589" t="n">
@@ -43916,7 +43916,7 @@
       </c>
       <c r="O590" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P590" t="n">
@@ -43991,7 +43991,7 @@
       </c>
       <c r="O591" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P591" t="n">
@@ -44066,7 +44066,7 @@
       </c>
       <c r="O592" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P592" t="n">
@@ -44141,7 +44141,7 @@
       </c>
       <c r="O593" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P593" t="n">
@@ -44278,7 +44278,7 @@
       </c>
       <c r="O595" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P595" t="n">
@@ -44353,7 +44353,7 @@
       </c>
       <c r="O596" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P596" t="n">
@@ -44428,7 +44428,7 @@
       </c>
       <c r="O597" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P597" t="n">
